--- a/data/OkFileDefinitions/TJXEWMS_StyleHeaderLayout.xlsx
+++ b/data/OkFileDefinitions/TJXEWMS_StyleHeaderLayout.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ticket_format</t>
+          <t>format</t>
         </is>
       </c>
       <c r="E6" t="n">
